--- a/docs/downloads/05/tbl_water_alaotra_ambatomanga.xlsx
+++ b/docs/downloads/05/tbl_water_alaotra_ambatomanga.xlsx
@@ -387,12 +387,6 @@
           <t>Cours d?eau</t>
         </is>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>5.9</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -441,12 +435,6 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2.9</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -579,12 +567,6 @@
         <is>
           <t>Alaotra - Tous</t>
         </is>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>
